--- a/data/trans_orig/IP07KS_C08_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C08_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de divertirse con sus amigos/as en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de divertirse con sus amigos/as, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67831</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59190</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75948</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40837</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34045</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47883</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69101</t>
+          <t>42740</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59605</t>
+          <t>35216</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76599</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>110571</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>97989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120372</t>
+          <t>121535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24819</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17773</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33622</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25685</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19234</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32644</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>37,81%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33417</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50011</t>
+          <t>52028</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>41059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61231</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4281</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8595</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5008</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>344</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5941</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5094</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>105576</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89965</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>120848</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>61,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>52,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>76878</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41446</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97585</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>53,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>107940</t>
+          <t>81033</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92018</t>
+          <t>70040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125551</t>
+          <t>90806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>184817</t>
+          <t>186609</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138750</t>
+          <t>169031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210916</t>
+          <t>205469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60277</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46055</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76813</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>63156</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41672</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99279</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59634</t>
+          <t>42043</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43449</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75853</t>
+          <t>53375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>122789</t>
+          <t>102320</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95642</t>
+          <t>84153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>170814</t>
+          <t>120190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10997</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2513</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6517</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2430</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1931</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125982</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315329</t>
+          <t>297563</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>173407</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>157428</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>190120</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>117715</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>73170</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>140342</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>177040</t>
+          <t>123774</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158353</t>
+          <t>111427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>195529</t>
+          <t>135159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>294755</t>
+          <t>297180</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239604</t>
+          <t>273982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320608</t>
+          <t>317365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>85097</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>69630</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>100837</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>88841</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>66360</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134984</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83959</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66763</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>172800</t>
+          <t>154348</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>133760</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232921</t>
+          <t>176391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16137</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7979</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197588</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>577</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
